--- a/detecno_fechas.xlsx
+++ b/detecno_fechas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG674"/>
+  <dimension ref="A1:AG702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88746,6 +88746,3674 @@
       </c>
       <c r="AG674" t="inlineStr"/>
     </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>18697</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>49441</v>
+      </c>
+      <c r="D675" t="n">
+        <v>4</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="K675" t="n">
+        <v>70977.56</v>
+      </c>
+      <c r="L675" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>2d125b66-daaf-4250-a894-6bac818fee23</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr"/>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr">
+        <is>
+          <t>2026/08/14</t>
+        </is>
+      </c>
+      <c r="T675" t="n">
+        <v>9790.01</v>
+      </c>
+      <c r="U675" t="inlineStr"/>
+      <c r="V675" t="n">
+        <v>1</v>
+      </c>
+      <c r="W675" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X675" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y675" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z675" t="n">
+        <v>70977.56</v>
+      </c>
+      <c r="AA675" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB675" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC675" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD675" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="AE675" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF675" t="inlineStr">
+        <is>
+          <t>E006325064</t>
+        </is>
+      </c>
+      <c r="AG675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>19114</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>49452</v>
+      </c>
+      <c r="D676" t="n">
+        <v>4</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>AVA150826T61</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>AZTECA VACUNAS</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K676" t="n">
+        <v>40931.45</v>
+      </c>
+      <c r="L676" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>2ded3c00-0adc-47d0-875a-ea429509c4d8</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr"/>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T676" t="n">
+        <v>5645.71</v>
+      </c>
+      <c r="U676" t="inlineStr"/>
+      <c r="V676" t="n">
+        <v>1</v>
+      </c>
+      <c r="W676" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X676" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y676" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z676" t="n">
+        <v>40931.45</v>
+      </c>
+      <c r="AA676" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB676" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC676" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD676" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE676" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF676" t="inlineStr">
+        <is>
+          <t>10092291</t>
+        </is>
+      </c>
+      <c r="AG676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>19115</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>49658</v>
+      </c>
+      <c r="D677" t="n">
+        <v>4</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K677" t="n">
+        <v>13670.27</v>
+      </c>
+      <c r="L677" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>2a5d7bc0-7834-4ac0-8070-812ca89e1e42</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr"/>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T677" t="n">
+        <v>1885.56</v>
+      </c>
+      <c r="U677" t="inlineStr"/>
+      <c r="V677" t="n">
+        <v>1</v>
+      </c>
+      <c r="W677" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X677" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y677" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z677" t="n">
+        <v>13670.27</v>
+      </c>
+      <c r="AA677" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB677" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC677" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD677" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE677" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF677" t="inlineStr">
+        <is>
+          <t>E006332709</t>
+        </is>
+      </c>
+      <c r="AG677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>19116</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>49656</v>
+      </c>
+      <c r="D678" t="n">
+        <v>4</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K678" t="n">
+        <v>12858.27</v>
+      </c>
+      <c r="L678" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>2346aba1-483a-4dcf-9557-d284bfc3ca48</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr"/>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q678" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T678" t="n">
+        <v>1773.56</v>
+      </c>
+      <c r="U678" t="inlineStr"/>
+      <c r="V678" t="n">
+        <v>1</v>
+      </c>
+      <c r="W678" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X678" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y678" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z678" t="n">
+        <v>12858.27</v>
+      </c>
+      <c r="AA678" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB678" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC678" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD678" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE678" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF678" t="inlineStr">
+        <is>
+          <t>E006332710</t>
+        </is>
+      </c>
+      <c r="AG678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>19117</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>49824</v>
+      </c>
+      <c r="D679" t="n">
+        <v>4</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K679" t="n">
+        <v>12858.27</v>
+      </c>
+      <c r="L679" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>6fe2ae18-3d72-48ee-bd35-47354c3a90a2</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr"/>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q679" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T679" t="n">
+        <v>1773.56</v>
+      </c>
+      <c r="U679" t="inlineStr"/>
+      <c r="V679" t="n">
+        <v>1</v>
+      </c>
+      <c r="W679" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X679" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y679" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z679" t="n">
+        <v>12858.27</v>
+      </c>
+      <c r="AA679" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB679" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC679" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD679" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE679" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF679" t="inlineStr">
+        <is>
+          <t>E006332700</t>
+        </is>
+      </c>
+      <c r="AG679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>19118</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>49822</v>
+      </c>
+      <c r="D680" t="n">
+        <v>4</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K680" t="n">
+        <v>12858.27</v>
+      </c>
+      <c r="L680" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>336bd384-f59e-4f82-a2d8-6f6cf3dd1338</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr"/>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q680" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T680" t="n">
+        <v>1773.56</v>
+      </c>
+      <c r="U680" t="inlineStr"/>
+      <c r="V680" t="n">
+        <v>1</v>
+      </c>
+      <c r="W680" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X680" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y680" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z680" t="n">
+        <v>12858.27</v>
+      </c>
+      <c r="AA680" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB680" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC680" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD680" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE680" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF680" t="inlineStr">
+        <is>
+          <t>E006332715</t>
+        </is>
+      </c>
+      <c r="AG680" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>19119</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>49798</v>
+      </c>
+      <c r="D681" t="n">
+        <v>4</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K681" t="n">
+        <v>21039.7</v>
+      </c>
+      <c r="L681" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>3289abf6-c4c2-4fa0-9282-8e2a8e3b1be1</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr"/>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q681" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T681" t="n">
+        <v>2902.03</v>
+      </c>
+      <c r="U681" t="inlineStr"/>
+      <c r="V681" t="n">
+        <v>1</v>
+      </c>
+      <c r="W681" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X681" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y681" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z681" t="n">
+        <v>21039.7</v>
+      </c>
+      <c r="AA681" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB681" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC681" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD681" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE681" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF681" t="inlineStr">
+        <is>
+          <t>E006332702</t>
+        </is>
+      </c>
+      <c r="AG681" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" t="n">
+        <v>19120</v>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>49773</v>
+      </c>
+      <c r="D682" t="n">
+        <v>4</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K682" t="n">
+        <v>20685.9</v>
+      </c>
+      <c r="L682" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>d84badf0-9272-4c19-879a-3a2289ac9df0</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr"/>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q682" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T682" t="n">
+        <v>2853.23</v>
+      </c>
+      <c r="U682" t="inlineStr"/>
+      <c r="V682" t="n">
+        <v>1</v>
+      </c>
+      <c r="W682" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X682" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y682" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z682" t="n">
+        <v>20685.9</v>
+      </c>
+      <c r="AA682" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB682" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC682" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD682" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE682" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF682" t="inlineStr">
+        <is>
+          <t>E006332704</t>
+        </is>
+      </c>
+      <c r="AG682" t="inlineStr"/>
+    </row>
+    <row r="683">
+      <c r="A683" t="n">
+        <v>19121</v>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>49772</v>
+      </c>
+      <c r="D683" t="n">
+        <v>4</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K683" t="n">
+        <v>20685.9</v>
+      </c>
+      <c r="L683" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>ca9ad7d9-867a-4d44-992c-de3430024c26</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr"/>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q683" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T683" t="n">
+        <v>2853.23</v>
+      </c>
+      <c r="U683" t="inlineStr"/>
+      <c r="V683" t="n">
+        <v>1</v>
+      </c>
+      <c r="W683" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X683" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y683" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z683" t="n">
+        <v>20685.9</v>
+      </c>
+      <c r="AA683" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB683" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC683" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD683" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE683" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF683" t="inlineStr">
+        <is>
+          <t>E006332706</t>
+        </is>
+      </c>
+      <c r="AG683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" t="n">
+        <v>19122</v>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>49795</v>
+      </c>
+      <c r="D684" t="n">
+        <v>4</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K684" t="n">
+        <v>12950.16</v>
+      </c>
+      <c r="L684" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>011a4ce3-ca2c-48b2-9200-e8b4bb23a809</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr"/>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q684" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T684" t="n">
+        <v>1786.23</v>
+      </c>
+      <c r="U684" t="inlineStr"/>
+      <c r="V684" t="n">
+        <v>1</v>
+      </c>
+      <c r="W684" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X684" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y684" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z684" t="n">
+        <v>12950.16</v>
+      </c>
+      <c r="AA684" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB684" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC684" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD684" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE684" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF684" t="inlineStr">
+        <is>
+          <t>E006332703</t>
+        </is>
+      </c>
+      <c r="AG684" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>19123</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>49771</v>
+      </c>
+      <c r="D685" t="n">
+        <v>4</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K685" t="n">
+        <v>20685.9</v>
+      </c>
+      <c r="L685" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>27653a3b-a13c-4dcc-ab81-896182873606</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr"/>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q685" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T685" t="n">
+        <v>2853.23</v>
+      </c>
+      <c r="U685" t="inlineStr"/>
+      <c r="V685" t="n">
+        <v>1</v>
+      </c>
+      <c r="W685" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X685" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y685" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z685" t="n">
+        <v>20685.9</v>
+      </c>
+      <c r="AA685" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB685" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC685" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD685" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE685" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF685" t="inlineStr">
+        <is>
+          <t>E006332708</t>
+        </is>
+      </c>
+      <c r="AG685" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" t="n">
+        <v>19125</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>49793</v>
+      </c>
+      <c r="D686" t="n">
+        <v>4</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K686" t="n">
+        <v>20685.9</v>
+      </c>
+      <c r="L686" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>bbde6942-2c76-402e-af97-af7117044bf3</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr"/>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q686" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T686" t="n">
+        <v>2853.23</v>
+      </c>
+      <c r="U686" t="inlineStr"/>
+      <c r="V686" t="n">
+        <v>1</v>
+      </c>
+      <c r="W686" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X686" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y686" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z686" t="n">
+        <v>20685.9</v>
+      </c>
+      <c r="AA686" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB686" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC686" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD686" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE686" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF686" t="inlineStr">
+        <is>
+          <t>E006332705</t>
+        </is>
+      </c>
+      <c r="AG686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" t="n">
+        <v>19126</v>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>49181</v>
+      </c>
+      <c r="D687" t="n">
+        <v>4</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K687" t="n">
+        <v>21911.88</v>
+      </c>
+      <c r="L687" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>5bf772dd-f8d9-403a-aada-83b86aade1bc</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr"/>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T687" t="n">
+        <v>3022.33</v>
+      </c>
+      <c r="U687" t="inlineStr"/>
+      <c r="V687" t="n">
+        <v>1</v>
+      </c>
+      <c r="W687" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X687" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y687" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z687" t="n">
+        <v>21911.88</v>
+      </c>
+      <c r="AA687" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB687" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC687" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD687" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE687" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF687" t="inlineStr">
+        <is>
+          <t>E006332714</t>
+        </is>
+      </c>
+      <c r="AG687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>19127</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>49636</v>
+      </c>
+      <c r="D688" t="n">
+        <v>4</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K688" t="n">
+        <v>18923.82</v>
+      </c>
+      <c r="L688" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>02ca9f13-e60c-49a4-9dc1-558ebb2d7e88</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr"/>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T688" t="n">
+        <v>2610.18</v>
+      </c>
+      <c r="U688" t="inlineStr"/>
+      <c r="V688" t="n">
+        <v>1</v>
+      </c>
+      <c r="W688" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X688" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y688" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z688" t="n">
+        <v>18923.82</v>
+      </c>
+      <c r="AA688" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB688" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC688" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD688" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE688" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF688" t="inlineStr">
+        <is>
+          <t>E006332711</t>
+        </is>
+      </c>
+      <c r="AG688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>19128</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>49770</v>
+      </c>
+      <c r="D689" t="n">
+        <v>4</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K689" t="n">
+        <v>9918.700000000001</v>
+      </c>
+      <c r="L689" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>f6790e1d-4653-4743-98e3-7774b9d031ee</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr"/>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T689" t="n">
+        <v>1368.1</v>
+      </c>
+      <c r="U689" t="inlineStr"/>
+      <c r="V689" t="n">
+        <v>1</v>
+      </c>
+      <c r="W689" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X689" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y689" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z689" t="n">
+        <v>9918.700000000001</v>
+      </c>
+      <c r="AA689" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB689" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC689" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD689" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE689" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF689" t="inlineStr">
+        <is>
+          <t>E006332707</t>
+        </is>
+      </c>
+      <c r="AG689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>19130</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>49821</v>
+      </c>
+      <c r="D690" t="n">
+        <v>4</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K690" t="n">
+        <v>19072.25</v>
+      </c>
+      <c r="L690" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>37b26d13-ab25-4516-ab03-9db548e69567</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr"/>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T690" t="n">
+        <v>2630.66</v>
+      </c>
+      <c r="U690" t="inlineStr"/>
+      <c r="V690" t="n">
+        <v>1</v>
+      </c>
+      <c r="W690" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X690" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y690" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z690" t="n">
+        <v>19072.25</v>
+      </c>
+      <c r="AA690" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB690" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC690" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD690" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE690" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF690" t="inlineStr">
+        <is>
+          <t>E006332719</t>
+        </is>
+      </c>
+      <c r="AG690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" t="n">
+        <v>19131</v>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>49831</v>
+      </c>
+      <c r="D691" t="n">
+        <v>4</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K691" t="n">
+        <v>27208.47</v>
+      </c>
+      <c r="L691" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>dd8148f5-1a57-4f09-bfe1-2e0599e2f7b8</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr"/>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T691" t="n">
+        <v>3752.9</v>
+      </c>
+      <c r="U691" t="inlineStr"/>
+      <c r="V691" t="n">
+        <v>1</v>
+      </c>
+      <c r="W691" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X691" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y691" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z691" t="n">
+        <v>27208.47</v>
+      </c>
+      <c r="AA691" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB691" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC691" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD691" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE691" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF691" t="inlineStr">
+        <is>
+          <t>E006332716</t>
+        </is>
+      </c>
+      <c r="AG691" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" t="n">
+        <v>19132</v>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>49896</v>
+      </c>
+      <c r="D692" t="n">
+        <v>4</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K692" t="n">
+        <v>21894.44</v>
+      </c>
+      <c r="L692" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>7d242e74-0941-4215-a22c-7f5878dcfe44</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr"/>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T692" t="n">
+        <v>3019.93</v>
+      </c>
+      <c r="U692" t="inlineStr"/>
+      <c r="V692" t="n">
+        <v>1</v>
+      </c>
+      <c r="W692" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X692" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y692" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z692" t="n">
+        <v>21894.44</v>
+      </c>
+      <c r="AA692" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB692" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC692" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD692" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE692" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF692" t="inlineStr">
+        <is>
+          <t>E006332701</t>
+        </is>
+      </c>
+      <c r="AG692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>19133</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>50125</v>
+      </c>
+      <c r="D693" t="n">
+        <v>4</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K693" t="n">
+        <v>96015.89</v>
+      </c>
+      <c r="L693" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>f493a15f-8ab2-408c-a335-b70095c1ddf7</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr"/>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="T693" t="n">
+        <v>13243.58</v>
+      </c>
+      <c r="U693" t="inlineStr"/>
+      <c r="V693" t="n">
+        <v>1</v>
+      </c>
+      <c r="W693" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X693" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y693" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z693" t="n">
+        <v>96015.89</v>
+      </c>
+      <c r="AA693" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB693" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC693" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD693" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE693" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF693" t="inlineStr">
+        <is>
+          <t>4500483949</t>
+        </is>
+      </c>
+      <c r="AG693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="n">
+        <v>19134</v>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>49999</v>
+      </c>
+      <c r="D694" t="n">
+        <v>4</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K694" t="n">
+        <v>123385.23</v>
+      </c>
+      <c r="L694" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>719fc77b-ddc6-4c68-859e-09905305b398</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr"/>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q694" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T694" t="n">
+        <v>17018.66</v>
+      </c>
+      <c r="U694" t="inlineStr"/>
+      <c r="V694" t="n">
+        <v>1</v>
+      </c>
+      <c r="W694" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X694" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y694" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z694" t="n">
+        <v>123385.23</v>
+      </c>
+      <c r="AA694" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB694" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC694" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD694" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE694" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF694" t="inlineStr">
+        <is>
+          <t>4500462983</t>
+        </is>
+      </c>
+      <c r="AG694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" t="n">
+        <v>19135</v>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>49551</v>
+      </c>
+      <c r="D695" t="n">
+        <v>4</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K695" t="n">
+        <v>207850.42</v>
+      </c>
+      <c r="L695" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>e15cf424-cb33-4856-804f-a5b1093a7d31</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr"/>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T695" t="n">
+        <v>28669.02</v>
+      </c>
+      <c r="U695" t="inlineStr"/>
+      <c r="V695" t="n">
+        <v>1</v>
+      </c>
+      <c r="W695" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X695" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y695" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z695" t="n">
+        <v>207850.42</v>
+      </c>
+      <c r="AA695" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB695" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC695" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD695" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE695" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF695" t="inlineStr">
+        <is>
+          <t>E006326885</t>
+        </is>
+      </c>
+      <c r="AG695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" t="n">
+        <v>19136</v>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>49512</v>
+      </c>
+      <c r="D696" t="n">
+        <v>4</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K696" t="n">
+        <v>40466.59</v>
+      </c>
+      <c r="L696" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>b94d18cf-9570-4ee0-be47-09ea324f9c52</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr"/>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T696" t="n">
+        <v>5581.6</v>
+      </c>
+      <c r="U696" t="inlineStr"/>
+      <c r="V696" t="n">
+        <v>1</v>
+      </c>
+      <c r="W696" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X696" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y696" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z696" t="n">
+        <v>40466.59</v>
+      </c>
+      <c r="AA696" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB696" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC696" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD696" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE696" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF696" t="inlineStr">
+        <is>
+          <t>E006332713</t>
+        </is>
+      </c>
+      <c r="AG696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="n">
+        <v>19137</v>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>49995</v>
+      </c>
+      <c r="D697" t="n">
+        <v>4</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K697" t="n">
+        <v>42486.92</v>
+      </c>
+      <c r="L697" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>29fff213-3f86-41bf-83c0-528cf03937e4</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr"/>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
+        </is>
+      </c>
+      <c r="T697" t="n">
+        <v>5860.27</v>
+      </c>
+      <c r="U697" t="inlineStr"/>
+      <c r="V697" t="n">
+        <v>1</v>
+      </c>
+      <c r="W697" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X697" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y697" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z697" t="n">
+        <v>42486.92</v>
+      </c>
+      <c r="AA697" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB697" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC697" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD697" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE697" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF697" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="n">
+        <v>19138</v>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>50035</v>
+      </c>
+      <c r="D698" t="n">
+        <v>4</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K698" t="n">
+        <v>127934.88</v>
+      </c>
+      <c r="L698" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>bd4eeb32-33f3-43a3-8f6b-2a71638b7534</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr"/>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="T698" t="n">
+        <v>17646.19</v>
+      </c>
+      <c r="U698" t="inlineStr"/>
+      <c r="V698" t="n">
+        <v>1</v>
+      </c>
+      <c r="W698" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X698" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y698" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z698" t="n">
+        <v>127934.88</v>
+      </c>
+      <c r="AA698" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB698" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC698" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD698" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE698" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF698" t="inlineStr">
+        <is>
+          <t>4500458230</t>
+        </is>
+      </c>
+      <c r="AG698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" t="n">
+        <v>19139</v>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>50053</v>
+      </c>
+      <c r="D699" t="n">
+        <v>4</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K699" t="n">
+        <v>78993.2</v>
+      </c>
+      <c r="L699" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>28ba7ec4-1ce1-4578-aa63-b7d8587d5f65</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr"/>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr">
+        <is>
+          <t>2026/08/19</t>
+        </is>
+      </c>
+      <c r="T699" t="n">
+        <v>10895.61</v>
+      </c>
+      <c r="U699" t="inlineStr"/>
+      <c r="V699" t="n">
+        <v>1</v>
+      </c>
+      <c r="W699" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X699" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y699" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z699" t="n">
+        <v>78993.2</v>
+      </c>
+      <c r="AA699" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB699" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC699" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD699" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE699" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF699" t="inlineStr">
+        <is>
+          <t>4500480141</t>
+        </is>
+      </c>
+      <c r="AG699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" t="n">
+        <v>19140</v>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>50122</v>
+      </c>
+      <c r="D700" t="n">
+        <v>4</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K700" t="n">
+        <v>56492.66</v>
+      </c>
+      <c r="L700" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>700d11a0-d9ec-48c1-8213-b0becadd3e8b</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr"/>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="T700" t="n">
+        <v>7792.09</v>
+      </c>
+      <c r="U700" t="inlineStr"/>
+      <c r="V700" t="n">
+        <v>1</v>
+      </c>
+      <c r="W700" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X700" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y700" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z700" t="n">
+        <v>56492.66</v>
+      </c>
+      <c r="AA700" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB700" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC700" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD700" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE700" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF700" t="inlineStr">
+        <is>
+          <t>4500480562</t>
+        </is>
+      </c>
+      <c r="AG700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" t="n">
+        <v>19141</v>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>50118</v>
+      </c>
+      <c r="D701" t="n">
+        <v>4</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K701" t="n">
+        <v>86393.83</v>
+      </c>
+      <c r="L701" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>dcacc4a3-64b5-4dfe-b99d-c82dd2e05a0a</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr"/>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr">
+        <is>
+          <t>2026/08/20</t>
+        </is>
+      </c>
+      <c r="T701" t="n">
+        <v>11916.39</v>
+      </c>
+      <c r="U701" t="inlineStr"/>
+      <c r="V701" t="n">
+        <v>1</v>
+      </c>
+      <c r="W701" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X701" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y701" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z701" t="n">
+        <v>86393.83</v>
+      </c>
+      <c r="AA701" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB701" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC701" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD701" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE701" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF701" t="inlineStr">
+        <is>
+          <t>4500480569</t>
+        </is>
+      </c>
+      <c r="AG701" t="inlineStr"/>
+    </row>
+    <row r="702">
+      <c r="A702" t="n">
+        <v>19142</v>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>50222</v>
+      </c>
+      <c r="D702" t="n">
+        <v>4</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="K702" t="n">
+        <v>202748.18</v>
+      </c>
+      <c r="L702" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>a1e34d93-b3ca-4908-9f96-1914ae77ca7e</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr"/>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q702" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="T702" t="n">
+        <v>27965.27</v>
+      </c>
+      <c r="U702" t="inlineStr"/>
+      <c r="V702" t="n">
+        <v>1</v>
+      </c>
+      <c r="W702" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X702" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y702" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z702" t="n">
+        <v>202748.18</v>
+      </c>
+      <c r="AA702" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB702" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC702" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD702" t="inlineStr">
+        <is>
+          <t>2026/08/21</t>
+        </is>
+      </c>
+      <c r="AE702" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF702" t="inlineStr">
+        <is>
+          <t>4500460559</t>
+        </is>
+      </c>
+      <c r="AG702" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/detecno_fechas.xlsx
+++ b/detecno_fechas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG702"/>
+  <dimension ref="A1:AG714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92414,6 +92414,1578 @@
       </c>
       <c r="AG702" t="inlineStr"/>
     </row>
+    <row r="703">
+      <c r="A703" t="n">
+        <v>19375</v>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>49956</v>
+      </c>
+      <c r="D703" t="n">
+        <v>4</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K703" t="n">
+        <v>13815.7</v>
+      </c>
+      <c r="L703" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>65afe28b-cde7-4b31-865e-4ff9980340df</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr"/>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q703" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr">
+        <is>
+          <t>2026/08/24</t>
+        </is>
+      </c>
+      <c r="T703" t="n">
+        <v>1905.61</v>
+      </c>
+      <c r="U703" t="inlineStr"/>
+      <c r="V703" t="n">
+        <v>1</v>
+      </c>
+      <c r="W703" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X703" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y703" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z703" t="n">
+        <v>13815.7</v>
+      </c>
+      <c r="AA703" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB703" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC703" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD703" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE703" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF703" t="inlineStr">
+        <is>
+          <t>E006338824</t>
+        </is>
+      </c>
+      <c r="AG703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" t="n">
+        <v>19376</v>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>50223</v>
+      </c>
+      <c r="D704" t="n">
+        <v>4</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K704" t="n">
+        <v>10365.63</v>
+      </c>
+      <c r="L704" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>951afa1e-9789-4653-ba64-858fde57e300</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr"/>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q704" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="T704" t="n">
+        <v>1429.74</v>
+      </c>
+      <c r="U704" t="inlineStr"/>
+      <c r="V704" t="n">
+        <v>1</v>
+      </c>
+      <c r="W704" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X704" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y704" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z704" t="n">
+        <v>10365.63</v>
+      </c>
+      <c r="AA704" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB704" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC704" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD704" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE704" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF704" t="inlineStr">
+        <is>
+          <t>E006342360</t>
+        </is>
+      </c>
+      <c r="AG704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="n">
+        <v>19377</v>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>50224</v>
+      </c>
+      <c r="D705" t="n">
+        <v>4</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K705" t="n">
+        <v>24440.21</v>
+      </c>
+      <c r="L705" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>467028fe-6e9f-4f5a-af68-0bbe6e33581a</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr"/>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="T705" t="n">
+        <v>3371.07</v>
+      </c>
+      <c r="U705" t="inlineStr"/>
+      <c r="V705" t="n">
+        <v>1</v>
+      </c>
+      <c r="W705" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X705" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y705" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z705" t="n">
+        <v>24440.21</v>
+      </c>
+      <c r="AA705" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB705" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC705" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD705" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE705" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF705" t="inlineStr">
+        <is>
+          <t>E006342359</t>
+        </is>
+      </c>
+      <c r="AG705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" t="n">
+        <v>19378</v>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>50285</v>
+      </c>
+      <c r="D706" t="n">
+        <v>4</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K706" t="n">
+        <v>18470.75</v>
+      </c>
+      <c r="L706" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>c7dee5b4-2ab3-4f77-81f8-a0c398802c04</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr"/>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q706" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="T706" t="n">
+        <v>2547.69</v>
+      </c>
+      <c r="U706" t="inlineStr"/>
+      <c r="V706" t="n">
+        <v>1</v>
+      </c>
+      <c r="W706" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X706" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y706" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z706" t="n">
+        <v>18470.75</v>
+      </c>
+      <c r="AA706" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB706" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC706" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD706" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE706" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF706" t="inlineStr">
+        <is>
+          <t>E006345858</t>
+        </is>
+      </c>
+      <c r="AG706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="n">
+        <v>19379</v>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>50284</v>
+      </c>
+      <c r="D707" t="n">
+        <v>4</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K707" t="n">
+        <v>11541.9</v>
+      </c>
+      <c r="L707" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>c00b54d3-10a1-48ee-b398-1e1b9ab8e056</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr"/>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="T707" t="n">
+        <v>1591.99</v>
+      </c>
+      <c r="U707" t="inlineStr"/>
+      <c r="V707" t="n">
+        <v>1</v>
+      </c>
+      <c r="W707" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X707" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y707" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z707" t="n">
+        <v>11541.9</v>
+      </c>
+      <c r="AA707" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB707" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC707" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD707" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE707" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF707" t="inlineStr">
+        <is>
+          <t>E006345859</t>
+        </is>
+      </c>
+      <c r="AG707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" t="n">
+        <v>19380</v>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>50299</v>
+      </c>
+      <c r="D708" t="n">
+        <v>4</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K708" t="n">
+        <v>6728</v>
+      </c>
+      <c r="L708" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>1ef7f917-62d3-486f-8353-eb0c70280b3d</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr"/>
+      <c r="P708" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q708" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R708" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S708" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="T708" t="n">
+        <v>928</v>
+      </c>
+      <c r="U708" t="inlineStr"/>
+      <c r="V708" t="n">
+        <v>1</v>
+      </c>
+      <c r="W708" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X708" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y708" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z708" t="n">
+        <v>6728</v>
+      </c>
+      <c r="AA708" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB708" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC708" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD708" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE708" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF708" t="inlineStr">
+        <is>
+          <t>E006345856</t>
+        </is>
+      </c>
+      <c r="AG708" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" t="n">
+        <v>19381</v>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>50312</v>
+      </c>
+      <c r="D709" t="n">
+        <v>4</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K709" t="n">
+        <v>83065.2</v>
+      </c>
+      <c r="L709" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>0ca7c0d9-bf1b-4f2f-9763-6bd07e8137e5</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr"/>
+      <c r="P709" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q709" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S709" t="inlineStr">
+        <is>
+          <t>2026/08/25</t>
+        </is>
+      </c>
+      <c r="T709" t="n">
+        <v>11457.27</v>
+      </c>
+      <c r="U709" t="inlineStr"/>
+      <c r="V709" t="n">
+        <v>1</v>
+      </c>
+      <c r="W709" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X709" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y709" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z709" t="n">
+        <v>83065.2</v>
+      </c>
+      <c r="AA709" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB709" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC709" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD709" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE709" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF709" t="inlineStr">
+        <is>
+          <t>4500479274</t>
+        </is>
+      </c>
+      <c r="AG709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" t="n">
+        <v>19382</v>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>50410</v>
+      </c>
+      <c r="D710" t="n">
+        <v>4</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K710" t="n">
+        <v>101082.85</v>
+      </c>
+      <c r="L710" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>2913a99d-adfe-413d-aa82-a61a45ea547a</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr"/>
+      <c r="P710" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q710" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R710" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S710" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="T710" t="n">
+        <v>13942.46</v>
+      </c>
+      <c r="U710" t="inlineStr"/>
+      <c r="V710" t="n">
+        <v>1</v>
+      </c>
+      <c r="W710" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X710" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y710" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z710" t="n">
+        <v>101082.85</v>
+      </c>
+      <c r="AA710" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB710" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC710" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD710" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE710" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF710" t="inlineStr">
+        <is>
+          <t>4500472366</t>
+        </is>
+      </c>
+      <c r="AG710" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" t="n">
+        <v>19383</v>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>50198</v>
+      </c>
+      <c r="D711" t="n">
+        <v>4</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K711" t="n">
+        <v>14644.25</v>
+      </c>
+      <c r="L711" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>b2070951-5848-4725-8364-3d6a3de4bdf9</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr"/>
+      <c r="P711" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q711" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R711" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S711" t="inlineStr">
+        <is>
+          <t>2026/08/26</t>
+        </is>
+      </c>
+      <c r="T711" t="n">
+        <v>2019.9</v>
+      </c>
+      <c r="U711" t="inlineStr"/>
+      <c r="V711" t="n">
+        <v>1</v>
+      </c>
+      <c r="W711" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X711" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y711" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z711" t="n">
+        <v>14644.25</v>
+      </c>
+      <c r="AA711" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB711" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC711" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD711" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE711" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF711" t="inlineStr">
+        <is>
+          <t>E006342361</t>
+        </is>
+      </c>
+      <c r="AG711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="n">
+        <v>19384</v>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>50513</v>
+      </c>
+      <c r="D712" t="n">
+        <v>4</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K712" t="n">
+        <v>7145.6</v>
+      </c>
+      <c r="L712" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>254b12fe-c46a-47ac-8441-8705cff2f830</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr"/>
+      <c r="P712" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q712" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R712" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S712" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="T712" t="n">
+        <v>985.6</v>
+      </c>
+      <c r="U712" t="inlineStr"/>
+      <c r="V712" t="n">
+        <v>1</v>
+      </c>
+      <c r="W712" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X712" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y712" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z712" t="n">
+        <v>7145.6</v>
+      </c>
+      <c r="AA712" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB712" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC712" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD712" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE712" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF712" t="inlineStr">
+        <is>
+          <t>4500483677</t>
+        </is>
+      </c>
+      <c r="AG712" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" t="n">
+        <v>19385</v>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>50282</v>
+      </c>
+      <c r="D713" t="n">
+        <v>4</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K713" t="n">
+        <v>17685.4</v>
+      </c>
+      <c r="L713" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>0c9590be-fdf5-4e17-afad-c2378b24aa71</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr"/>
+      <c r="P713" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q713" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R713" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S713" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="T713" t="n">
+        <v>2439.37</v>
+      </c>
+      <c r="U713" t="inlineStr"/>
+      <c r="V713" t="n">
+        <v>1</v>
+      </c>
+      <c r="W713" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X713" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y713" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z713" t="n">
+        <v>17685.4</v>
+      </c>
+      <c r="AA713" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB713" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC713" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD713" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE713" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF713" t="inlineStr">
+        <is>
+          <t>E006345860</t>
+        </is>
+      </c>
+      <c r="AG713" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" t="n">
+        <v>19386</v>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>50296</v>
+      </c>
+      <c r="D714" t="n">
+        <v>4</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="K714" t="n">
+        <v>6728</v>
+      </c>
+      <c r="L714" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>6ad469da-6dd3-4d7f-9890-c3016a9758f0</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr"/>
+      <c r="P714" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q714" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R714" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S714" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="T714" t="n">
+        <v>928</v>
+      </c>
+      <c r="U714" t="inlineStr"/>
+      <c r="V714" t="n">
+        <v>1</v>
+      </c>
+      <c r="W714" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X714" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y714" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z714" t="n">
+        <v>6728</v>
+      </c>
+      <c r="AA714" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB714" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC714" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD714" t="inlineStr">
+        <is>
+          <t>2026/08/28</t>
+        </is>
+      </c>
+      <c r="AE714" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF714" t="inlineStr">
+        <is>
+          <t>E006345857</t>
+        </is>
+      </c>
+      <c r="AG714" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/detecno_fechas.xlsx
+++ b/detecno_fechas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG714"/>
+  <dimension ref="A1:AG731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93986,6 +93986,2233 @@
       </c>
       <c r="AG714" t="inlineStr"/>
     </row>
+    <row r="715">
+      <c r="A715" t="n">
+        <v>19572</v>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>50298</v>
+      </c>
+      <c r="D715" t="n">
+        <v>4</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>AVA150826T61</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>AZTECA VACUNAS</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K715" t="n">
+        <v>6728</v>
+      </c>
+      <c r="L715" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>4c956a33-513f-4bd0-b67e-95da954364fe</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr"/>
+      <c r="P715" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q715" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R715" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S715" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="T715" t="n">
+        <v>928</v>
+      </c>
+      <c r="U715" t="inlineStr"/>
+      <c r="V715" t="n">
+        <v>1</v>
+      </c>
+      <c r="W715" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X715" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y715" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z715" t="n">
+        <v>6728</v>
+      </c>
+      <c r="AA715" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB715" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC715" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD715" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE715" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF715" t="inlineStr">
+        <is>
+          <t>E006348983</t>
+        </is>
+      </c>
+      <c r="AG715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="n">
+        <v>19573</v>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>50415</v>
+      </c>
+      <c r="D716" t="n">
+        <v>4</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K716" t="n">
+        <v>20008.92</v>
+      </c>
+      <c r="L716" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>b01fd6a2-9ff6-4d5a-a4ae-88a1ef023575</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr"/>
+      <c r="P716" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q716" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R716" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S716" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="T716" t="n">
+        <v>2759.85</v>
+      </c>
+      <c r="U716" t="inlineStr"/>
+      <c r="V716" t="n">
+        <v>1</v>
+      </c>
+      <c r="W716" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X716" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y716" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z716" t="n">
+        <v>20008.92</v>
+      </c>
+      <c r="AA716" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB716" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC716" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD716" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE716" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF716" t="inlineStr">
+        <is>
+          <t>E006348985</t>
+        </is>
+      </c>
+      <c r="AG716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" t="n">
+        <v>19574</v>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>50512</v>
+      </c>
+      <c r="D717" t="n">
+        <v>4</v>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K717" t="n">
+        <v>21884.38</v>
+      </c>
+      <c r="L717" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>a26efb0b-637f-4c84-bad7-3fbe1d20d979</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr"/>
+      <c r="P717" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q717" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R717" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S717" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="T717" t="n">
+        <v>3018.54</v>
+      </c>
+      <c r="U717" t="inlineStr"/>
+      <c r="V717" t="n">
+        <v>1</v>
+      </c>
+      <c r="W717" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X717" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y717" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z717" t="n">
+        <v>21884.38</v>
+      </c>
+      <c r="AA717" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB717" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC717" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD717" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE717" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF717" t="inlineStr">
+        <is>
+          <t>E006348987</t>
+        </is>
+      </c>
+      <c r="AG717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="n">
+        <v>19575</v>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>50572</v>
+      </c>
+      <c r="D718" t="n">
+        <v>4</v>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K718" t="n">
+        <v>15967.12</v>
+      </c>
+      <c r="L718" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>7b9727fd-d5da-4ce4-901c-f397b003678a</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr"/>
+      <c r="P718" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q718" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R718" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S718" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="T718" t="n">
+        <v>2202.37</v>
+      </c>
+      <c r="U718" t="inlineStr"/>
+      <c r="V718" t="n">
+        <v>1</v>
+      </c>
+      <c r="W718" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X718" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y718" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z718" t="n">
+        <v>15967.12</v>
+      </c>
+      <c r="AA718" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB718" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC718" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD718" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE718" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF718" t="inlineStr">
+        <is>
+          <t>E006350642</t>
+        </is>
+      </c>
+      <c r="AG718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="n">
+        <v>19576</v>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>50636</v>
+      </c>
+      <c r="D719" t="n">
+        <v>4</v>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K719" t="n">
+        <v>17685.4</v>
+      </c>
+      <c r="L719" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>c0ba297f-bbfb-4f70-8a80-f968957bf7a8</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr"/>
+      <c r="P719" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q719" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R719" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S719" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="T719" t="n">
+        <v>2439.37</v>
+      </c>
+      <c r="U719" t="inlineStr"/>
+      <c r="V719" t="n">
+        <v>1</v>
+      </c>
+      <c r="W719" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X719" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y719" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z719" t="n">
+        <v>17685.4</v>
+      </c>
+      <c r="AA719" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB719" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC719" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD719" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE719" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF719" t="inlineStr">
+        <is>
+          <t>E006352349</t>
+        </is>
+      </c>
+      <c r="AG719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="n">
+        <v>19577</v>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>50637</v>
+      </c>
+      <c r="D720" t="n">
+        <v>4</v>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K720" t="n">
+        <v>17685.4</v>
+      </c>
+      <c r="L720" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>56595d64-c9a5-4abf-8751-20aa983988e0</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr"/>
+      <c r="P720" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q720" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S720" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="T720" t="n">
+        <v>2439.37</v>
+      </c>
+      <c r="U720" t="inlineStr"/>
+      <c r="V720" t="n">
+        <v>1</v>
+      </c>
+      <c r="W720" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X720" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y720" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z720" t="n">
+        <v>17685.4</v>
+      </c>
+      <c r="AA720" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB720" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC720" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD720" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE720" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF720" t="inlineStr">
+        <is>
+          <t>E006352358</t>
+        </is>
+      </c>
+      <c r="AG720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="n">
+        <v>19578</v>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>50631</v>
+      </c>
+      <c r="D721" t="n">
+        <v>4</v>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K721" t="n">
+        <v>137904.91</v>
+      </c>
+      <c r="L721" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>006e10e1-570e-4471-8342-d0a417bca093</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr"/>
+      <c r="P721" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q721" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S721" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="T721" t="n">
+        <v>19021.37</v>
+      </c>
+      <c r="U721" t="inlineStr"/>
+      <c r="V721" t="n">
+        <v>1</v>
+      </c>
+      <c r="W721" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X721" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y721" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z721" t="n">
+        <v>137904.91</v>
+      </c>
+      <c r="AA721" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB721" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC721" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD721" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE721" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF721" t="inlineStr">
+        <is>
+          <t>4500460814</t>
+        </is>
+      </c>
+      <c r="AG721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" t="n">
+        <v>19579</v>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>50633</v>
+      </c>
+      <c r="D722" t="n">
+        <v>4</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K722" t="n">
+        <v>128430.03</v>
+      </c>
+      <c r="L722" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>c5b06034-7454-45e0-b1c3-729bbb5b804d</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr"/>
+      <c r="P722" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q722" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R722" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S722" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="T722" t="n">
+        <v>17714.49</v>
+      </c>
+      <c r="U722" t="inlineStr"/>
+      <c r="V722" t="n">
+        <v>1</v>
+      </c>
+      <c r="W722" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X722" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y722" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z722" t="n">
+        <v>128430.03</v>
+      </c>
+      <c r="AA722" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB722" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC722" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD722" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE722" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF722" t="inlineStr">
+        <is>
+          <t>4500464707</t>
+        </is>
+      </c>
+      <c r="AG722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="n">
+        <v>19580</v>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>50095</v>
+      </c>
+      <c r="D723" t="n">
+        <v>4</v>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K723" t="n">
+        <v>4881.23</v>
+      </c>
+      <c r="L723" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>6cf8b06c-79c9-4ddd-8b22-d50ff9915b06</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr"/>
+      <c r="P723" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q723" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R723" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S723" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="T723" t="n">
+        <v>673.27</v>
+      </c>
+      <c r="U723" t="inlineStr"/>
+      <c r="V723" t="n">
+        <v>1</v>
+      </c>
+      <c r="W723" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X723" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y723" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z723" t="n">
+        <v>4881.23</v>
+      </c>
+      <c r="AA723" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB723" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC723" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD723" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE723" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF723" t="inlineStr">
+        <is>
+          <t>E006348990</t>
+        </is>
+      </c>
+      <c r="AG723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>19581</v>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>50413</v>
+      </c>
+      <c r="D724" t="n">
+        <v>4</v>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K724" t="n">
+        <v>19460.46</v>
+      </c>
+      <c r="L724" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>aa327423-2675-4896-b2d2-aae586435b18</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr"/>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q724" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R724" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S724" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="T724" t="n">
+        <v>2684.2</v>
+      </c>
+      <c r="U724" t="inlineStr"/>
+      <c r="V724" t="n">
+        <v>1</v>
+      </c>
+      <c r="W724" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X724" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y724" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z724" t="n">
+        <v>19460.46</v>
+      </c>
+      <c r="AA724" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB724" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC724" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD724" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE724" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF724" t="inlineStr">
+        <is>
+          <t>E006348986</t>
+        </is>
+      </c>
+      <c r="AG724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>19582</v>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>50564</v>
+      </c>
+      <c r="D725" t="n">
+        <v>4</v>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K725" t="n">
+        <v>27242.18</v>
+      </c>
+      <c r="L725" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>246e56be-e91a-441b-abf1-28ccd06e20e1</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr"/>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q725" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R725" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S725" t="inlineStr">
+        <is>
+          <t>2026/09/02</t>
+        </is>
+      </c>
+      <c r="T725" t="n">
+        <v>3757.54</v>
+      </c>
+      <c r="U725" t="inlineStr"/>
+      <c r="V725" t="n">
+        <v>1</v>
+      </c>
+      <c r="W725" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X725" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y725" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z725" t="n">
+        <v>27242.18</v>
+      </c>
+      <c r="AA725" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB725" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC725" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD725" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE725" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF725" t="inlineStr">
+        <is>
+          <t>E006350644</t>
+        </is>
+      </c>
+      <c r="AG725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>19583</v>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>50472</v>
+      </c>
+      <c r="D726" t="n">
+        <v>4</v>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K726" t="n">
+        <v>7305.63</v>
+      </c>
+      <c r="L726" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>3dfa5719-1985-42e7-b580-7744f2bada14</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr"/>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q726" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R726" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S726" t="inlineStr">
+        <is>
+          <t>2026/09/01</t>
+        </is>
+      </c>
+      <c r="T726" t="n">
+        <v>1007.67</v>
+      </c>
+      <c r="U726" t="inlineStr"/>
+      <c r="V726" t="n">
+        <v>1</v>
+      </c>
+      <c r="W726" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X726" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y726" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z726" t="n">
+        <v>7305.63</v>
+      </c>
+      <c r="AA726" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB726" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC726" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD726" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE726" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF726" t="inlineStr">
+        <is>
+          <t>E006348988</t>
+        </is>
+      </c>
+      <c r="AG726" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>19584</v>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>50749</v>
+      </c>
+      <c r="D727" t="n">
+        <v>4</v>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K727" t="n">
+        <v>129508.51</v>
+      </c>
+      <c r="L727" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>a4f4bde7-4c2b-49ab-8538-04c530804d4d</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr"/>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q727" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R727" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S727" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="T727" t="n">
+        <v>17863.24</v>
+      </c>
+      <c r="U727" t="inlineStr"/>
+      <c r="V727" t="n">
+        <v>1</v>
+      </c>
+      <c r="W727" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X727" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y727" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z727" t="n">
+        <v>129508.51</v>
+      </c>
+      <c r="AA727" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB727" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC727" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD727" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE727" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF727" t="inlineStr">
+        <is>
+          <t>4500462199</t>
+        </is>
+      </c>
+      <c r="AG727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" t="n">
+        <v>19585</v>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>50750</v>
+      </c>
+      <c r="D728" t="n">
+        <v>4</v>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K728" t="n">
+        <v>49014.8</v>
+      </c>
+      <c r="L728" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>080e9e65-1a39-452b-9011-79088ec7d793</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr"/>
+      <c r="P728" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q728" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S728" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="T728" t="n">
+        <v>6760.66</v>
+      </c>
+      <c r="U728" t="inlineStr"/>
+      <c r="V728" t="n">
+        <v>1</v>
+      </c>
+      <c r="W728" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X728" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y728" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z728" t="n">
+        <v>49014.8</v>
+      </c>
+      <c r="AA728" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB728" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC728" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD728" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE728" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF728" t="inlineStr">
+        <is>
+          <t>4500483424</t>
+        </is>
+      </c>
+      <c r="AG728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" t="n">
+        <v>19586</v>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>50700</v>
+      </c>
+      <c r="D729" t="n">
+        <v>4</v>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K729" t="n">
+        <v>46543.2</v>
+      </c>
+      <c r="L729" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>639c619c-0186-41c8-bc96-609c3ce38181</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr"/>
+      <c r="P729" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q729" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R729" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S729" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="T729" t="n">
+        <v>6419.75</v>
+      </c>
+      <c r="U729" t="inlineStr"/>
+      <c r="V729" t="n">
+        <v>1</v>
+      </c>
+      <c r="W729" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X729" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y729" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z729" t="n">
+        <v>46543.2</v>
+      </c>
+      <c r="AA729" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB729" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC729" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD729" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE729" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF729" t="inlineStr">
+        <is>
+          <t>4500485292</t>
+        </is>
+      </c>
+      <c r="AG729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" t="n">
+        <v>19587</v>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>50707</v>
+      </c>
+      <c r="D730" t="n">
+        <v>4</v>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>SPA960328P62</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>SANOFI PASTEUR</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K730" t="n">
+        <v>28284.47</v>
+      </c>
+      <c r="L730" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>d8ffb7a1-1c06-4688-9cf6-0b8fd7b37873</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr"/>
+      <c r="P730" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q730" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R730" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S730" t="inlineStr">
+        <is>
+          <t>2026/09/03</t>
+        </is>
+      </c>
+      <c r="T730" t="n">
+        <v>3901.31</v>
+      </c>
+      <c r="U730" t="inlineStr"/>
+      <c r="V730" t="n">
+        <v>1</v>
+      </c>
+      <c r="W730" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X730" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y730" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z730" t="n">
+        <v>28284.47</v>
+      </c>
+      <c r="AA730" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB730" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC730" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD730" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE730" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF730" t="inlineStr">
+        <is>
+          <t>4500487967</t>
+        </is>
+      </c>
+      <c r="AG730" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>19588</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>50676</v>
+      </c>
+      <c r="D731" t="n">
+        <v>4</v>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>NSA990325BB9</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>ABSOLUTE BROKERAGE CUSTOMS</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>SME2406244T2</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>SANOFI MEXICO</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="K731" t="n">
+        <v>19424.5</v>
+      </c>
+      <c r="L731" t="n">
+        <v>100537273</v>
+      </c>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>PPD</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>0053d8c4-5252-4e85-9b3b-3eeeee5dc8fc</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr"/>
+      <c r="P731" t="inlineStr">
+        <is>
+          <t>Valido Fiscal</t>
+        </is>
+      </c>
+      <c r="Q731" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="R731" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="S731" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="T731" t="n">
+        <v>2679.24</v>
+      </c>
+      <c r="U731" t="inlineStr"/>
+      <c r="V731" t="n">
+        <v>1</v>
+      </c>
+      <c r="W731" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="X731" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y731" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z731" t="n">
+        <v>19424.5</v>
+      </c>
+      <c r="AA731" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+      <c r="AB731" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC731" t="inlineStr">
+        <is>
+          <t>Confiable</t>
+        </is>
+      </c>
+      <c r="AD731" t="inlineStr">
+        <is>
+          <t>2026/09/04</t>
+        </is>
+      </c>
+      <c r="AE731" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF731" t="inlineStr">
+        <is>
+          <t>E006354202</t>
+        </is>
+      </c>
+      <c r="AG731" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
